--- a/AAII_Financials/Quarterly/BWA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWA_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3648000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3533000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3572000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3591000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3638000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3515000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3439000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3449000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3603000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3595000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3522000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3622000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3671000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3383000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3317000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3226000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6092000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3874000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3655000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3416000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3758000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4009000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3926000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2534000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3705000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2279000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2559000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2492000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2551000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2566000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2572800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2478500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2694000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2784300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2586400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2416200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2389700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2407000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2259000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2214200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2927000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2856000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2832000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2948000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2998000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2869000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2756000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2813000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2918000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2951000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2863000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2970000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2991000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2806000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2678000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2619000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4969000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3124000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3030000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2766000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2996000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3191000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3154000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2017000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3084000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1832000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2014000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1968000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2038000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2047000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2030000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1962900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2114800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2192500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2021600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1894600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1875500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1889700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1758000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1743500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E10" s="3">
         <v>677000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>740000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>643000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>640000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>646000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>683000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>636000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>685000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>644000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>659000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>652000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>680000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>577000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>639000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>607000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1123000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>750000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>625000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>650000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>762000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>818000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>772000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>517000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>621000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>447000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>545000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>524000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>513000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>519000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>542800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>515600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>579200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>591800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>564800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>521600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>514200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>517300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>501000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>470700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>191000</v>
+      </c>
+      <c r="E12" s="3">
         <v>177000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>214000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>206000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>207000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>182000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>216000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>218000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>220000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>218000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>-541000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>192000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>213000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>166000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>167000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>178000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>356000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>191000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>174000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>184000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>166000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>183000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>179000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>100000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>197000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>109000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>94000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>102000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>113000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>104000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>103000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>108000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>112400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>116700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>104700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>101500</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>104900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>96400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>84300</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,180 +1496,186 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E14" s="3">
         <v>19000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>642000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>56000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>36000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>96000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>654000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>20000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>51000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>69000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>85000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>69000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>34000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>21000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>56000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>58000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>84000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>41000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>160000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>33000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>105000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>45000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-138000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>18000</v>
       </c>
       <c r="AE14" s="3">
         <v>18000</v>
       </c>
       <c r="AF14" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AG14" s="3">
         <v>15000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>68100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>119800</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>19700</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>5300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-89100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>113700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E15" s="3">
         <v>143000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>157000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>159000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>158000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>155000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>163000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>158000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>152000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>150000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>151000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>143000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>142000</v>
       </c>
       <c r="P15" s="3">
         <v>142000</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>142000</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>17</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>17</v>
@@ -1669,11 +1692,11 @@
       <c r="X15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z15" s="3">
         <v>38000</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>17</v>
@@ -1690,8 +1713,8 @@
       <c r="AE15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>3260000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3183000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3170000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3289000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3314000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3183000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3098000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3158000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3258000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3282000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3224000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3300000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3326000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3099000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3052000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2961000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5613000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3522000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3477000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3163000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3441000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3606000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3703000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2250000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3585000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2090000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2081000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2216000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2266000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2302000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2307200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2200500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2381200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2450800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2378600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2141600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2090200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2114300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2717000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2063900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>388000</v>
+      </c>
+      <c r="E18" s="3">
         <v>350000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>402000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>302000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>324000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>332000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>341000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>291000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>345000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>313000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>298000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>322000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>345000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>284000</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>265000</v>
       </c>
       <c r="R18" s="3">
         <v>265000</v>
       </c>
       <c r="S18" s="3">
+        <v>265000</v>
+      </c>
+      <c r="T18" s="3">
         <v>479000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>352000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>178000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>253000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>317000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>403000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>223000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>284000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>120000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>189000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>478000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>276000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>285000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>264000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>265600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>278000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>312800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>333500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>207800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>274600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>299500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>292700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-458000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-8000</v>
       </c>
       <c r="H20" s="3">
         <v>-8000</v>
       </c>
       <c r="I20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-33000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-36000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>27000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-246000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>396000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>8000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>24000</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>9000</v>
       </c>
       <c r="AC20" s="3">
         <v>9000</v>
       </c>
       <c r="AD20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="AE20" s="3">
         <v>12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>12000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>19100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>16800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>14300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>15500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>17000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>15800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>11200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>12900</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-8400</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>540000</v>
+      </c>
+      <c r="E21" s="3">
         <v>501000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>565000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>472000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>490000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>495000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>508000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>455000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>509000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>468000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>456000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>475000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>499000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>426000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>372000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>323000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>841000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>514000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>363000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>412000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>539000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>352000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>848000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>407000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>368000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>310000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>602000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>398000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>376000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>383000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>385600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>404600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>438700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>457000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>329100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>396500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>415100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>401200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-344900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>239700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2305,365 +2345,374 @@
         <v>25000</v>
       </c>
       <c r="E22" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F22" s="3">
         <v>22000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>28000</v>
       </c>
       <c r="I22" s="3">
         <v>28000</v>
       </c>
       <c r="J22" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K22" s="3">
         <v>24000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>17000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>37000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>21000</v>
       </c>
       <c r="V22" s="3">
         <v>21000</v>
       </c>
       <c r="W22" s="3">
+        <v>21000</v>
+      </c>
+      <c r="X22" s="3">
         <v>42000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>21000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>48000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>12000</v>
       </c>
       <c r="AC22" s="3">
         <v>12000</v>
       </c>
       <c r="AD22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>15000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>14000</v>
       </c>
       <c r="AF22" s="3">
         <v>14000</v>
       </c>
       <c r="AG22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AH22" s="3">
         <v>13300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>16100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>16900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>17600</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>18000</v>
       </c>
       <c r="AN22" s="3">
         <v>18000</v>
       </c>
       <c r="AO22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="AP22" s="3">
         <v>19500</v>
       </c>
-      <c r="AP22" s="3" t="s">
+      <c r="AQ22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E23" s="3">
         <v>328000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-240000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>248000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>284000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>232000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-319000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>270000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>298000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>290000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>229000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>238000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>276000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>248000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>214000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>260000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>439000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>315000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>155000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>196000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>302000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>136000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>596000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>272000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>96000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>186000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>475000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>273000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>255000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>262000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>266800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>282700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>314700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>331700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>206400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>274000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>297300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>285900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-464600</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>141900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E24" s="3">
         <v>73000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-31000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>59000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>133000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>30000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>67000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>18000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>68000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>109000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>91000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>79000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>211000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>143000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>49000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>238000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>66000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>73000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>69000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>73400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>43800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>94900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>64900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>79400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>76200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>86300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-183100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>48800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>291000</v>
+      </c>
+      <c r="E26" s="3">
         <v>255000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-241000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>173000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>232000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>171000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-386000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>257000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>329000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>228000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>170000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>105000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>246000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>181000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>196000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>192000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>330000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>224000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>154000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>117000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>274000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>94000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>385000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>129000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>53000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>137000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>237000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>207000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>182000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>193000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>255000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>209300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>270900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>236800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>141500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>194600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>221100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>199600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-281500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E27" s="3">
         <v>242000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-262000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>158000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>224000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>157000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-405000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>234000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>303000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>206000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>154000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>50000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>204000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>172000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>173000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>291000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>129000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>96000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>247000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>65000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>358000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>111000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>31000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>129000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>220000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>194000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>172000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>182000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>237400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>197200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>258400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>225100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>127300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>184900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>212000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>189200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-293300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3171,44 +3232,44 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-8000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-12000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-7000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-37000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-24000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>49000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>83000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>100000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>125000</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
@@ -3221,8 +3282,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>17</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>17</v>
@@ -3230,8 +3291,8 @@
       <c r="AB29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3240,25 +3301,25 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-7400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>6600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>13400</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-273500</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>17</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>8000</v>
       </c>
       <c r="H32" s="3">
         <v>8000</v>
       </c>
       <c r="I32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>33000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>36000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-27000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>246000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-396000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-24000</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-9000</v>
       </c>
       <c r="AC32" s="3">
         <v>-9000</v>
       </c>
       <c r="AD32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>16000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-19100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-16800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-15500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-17000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-15800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-11200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-12900</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>8400</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E33" s="3">
         <v>242000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-262000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>158000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>224000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>157000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-405000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>234000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>303000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>206000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>154000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>50000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>204000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>217000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>255000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>273000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>416000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>129000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>96000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>247000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>65000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>358000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>111000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>129000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>220000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>194000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>172000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>160000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>230000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>203800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>225100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-146200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>184900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>212000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>189200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-293300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E35" s="3">
         <v>242000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-262000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>158000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>224000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>157000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-405000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>234000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>303000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>206000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>154000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>50000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>204000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>217000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>255000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>273000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>416000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>129000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>96000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>247000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>65000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>358000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>111000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>129000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>220000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>194000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>172000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>160000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>230000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>203800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>225100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-146200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>184900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>212000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>189200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-293300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2448000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2110000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2313000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2172000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2041000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1707000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2094000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2000000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1288000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1037000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1534000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>949000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>848000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>950000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1083000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1241000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1390000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1501000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1841000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1507000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1553000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1755000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1650000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2121000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2003000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>901000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>832000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>916000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>710000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>494000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>739400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>361800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>361900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>409700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>545300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>414300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>387100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>358400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>443700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>518700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,862 +4553,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3093000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3103000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2977000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3275000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3213000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3157000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2858000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3231000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3127000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3305000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3127000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3367000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3871000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3580000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2485000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3381000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3152000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3185000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2915000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2911000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3085000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3168000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2919000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1977000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1535000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1735000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1931000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1993000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2073000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2076000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1987400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2071600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2131000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2247100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2018900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2046100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1939300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1934300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1689300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1764000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1200000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1207000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1231000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1216000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1205000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1251000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1366000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1322000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1333000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1313000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1328000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1860000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1800000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1217000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1658000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1653000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1644000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1534000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1649000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1567000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1361000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1286000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>815000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>836000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>847000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>807000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>810000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>817000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>807000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>780800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>810300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>800200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>800400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>766300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>773400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>701400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>656900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>641200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>687200</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E45" s="3">
         <v>225000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>182000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>198000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>218000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>147000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>209000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>217000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>226000</v>
       </c>
       <c r="L45" s="3">
         <v>226000</v>
       </c>
       <c r="M45" s="3">
+        <v>226000</v>
+      </c>
+      <c r="N45" s="3">
         <v>148000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>216000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>262000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>146000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1875000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>267000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>285000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>310000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>307000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>395000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>332000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>298000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>312000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>252000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>267000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>258000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>266000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>268000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>249000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>342000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>297000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>246900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>250600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>240600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>212700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>167300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>165400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>157700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>137400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>319300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7088000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6742000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6795000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6978000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6778000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6379000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6521000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6856000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6004000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5957000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6217000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5900000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6876000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6607000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6617000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6547000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6480000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6640000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6597000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6462000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6537000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6582000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6167000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5165000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4641000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3741000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3836000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3987000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3849000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3719000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3804600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3490600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3543700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3697800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3543200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3401100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3193200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3107300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2911600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3289200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300000</v>
+      </c>
+      <c r="E47" s="3">
         <v>309000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>310000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>329000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>310000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>314000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>315000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>312000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>290000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>310000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>308000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>567000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>738000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>803000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>819000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>422000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>442000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>473000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>530000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>513000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>546000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>557000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>820000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>305000</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>315000</v>
       </c>
       <c r="AB47" s="3">
         <v>315000</v>
       </c>
       <c r="AC47" s="3">
+        <v>315000</v>
+      </c>
+      <c r="AD47" s="3">
         <v>318000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>694000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>690000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>617000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>591700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>610300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>610500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>581800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>547400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>559500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>528600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>530000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>502200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>512700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3408000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3443000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3481000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3630000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3767000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3726000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3752000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3956000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3878000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3903000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3926000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3697000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4669000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4660000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8096000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4190000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4327000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4521000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4580000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4598000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4744000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4668000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4591000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2824000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2781000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2839000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3010000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2900000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2986000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2993000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2903800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2827800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2825700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2923800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2863800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2753700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2663800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2553100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2501800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>2518500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2402000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2420000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2449000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2872000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2897000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2822000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2831000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3541000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3486000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3517000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3577000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3493000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4406000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4453000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3597000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4320000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4367000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4535000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4370000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4419000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4497000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3655000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3723000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2226000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2205000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2201000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2244000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2222000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2266000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2281000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2292900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2306600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2320000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2375800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2374500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2391500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2188500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2163800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2165700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2224900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>179000</v>
+      </c>
+      <c r="E52" s="3">
         <v>175000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>178000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>180000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>155000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>170000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>215000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>139000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>182000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>179000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>168000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>254000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>293000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>314000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2429000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>598000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>528000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>509000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>498000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>499000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>539000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>509000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>728000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>372000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>395000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>406000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>294000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>396000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>440000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>494000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>502300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>481100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>477300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>455600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>458700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>710400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>714400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>729500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>753400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>462000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13934000</v>
+      </c>
+      <c r="E54" s="3">
         <v>13653000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13769000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14496000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14399000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13830000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13993000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15137000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14108000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14122000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14453000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14104000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17317000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17117000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16994000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16077000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16144000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16678000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16575000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16491000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16863000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15971000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16029000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10892000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10337000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9502000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9702000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10199000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10231000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10104000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10095300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9716400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9777200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10034800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9787600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9816200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9288500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9083700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8834700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9007300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2138000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2058000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1996000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2101000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2093000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2060000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2032000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2176000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2202000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2378000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2546000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2396000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2725000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2676000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2146000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2298000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2465000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2276000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2131000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2367000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2485000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2352000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2115000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1642000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1776000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1948000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2014000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2052000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2021000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2128900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2001300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2117500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2149900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2260300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2002500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1896100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1839000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>3692300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1757800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E58" s="3">
         <v>42000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>41000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>98000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>436000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>434000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>481000</v>
       </c>
       <c r="L58" s="3">
         <v>481000</v>
       </c>
       <c r="M58" s="3">
+        <v>481000</v>
+      </c>
+      <c r="N58" s="3">
         <v>110000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>104000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>105000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>104000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>64000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>56000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>60000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>64000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>66000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>54000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>13000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>51000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>49000</v>
       </c>
       <c r="Z58" s="3">
         <v>49000</v>
       </c>
       <c r="AA58" s="3">
+        <v>49000</v>
+      </c>
+      <c r="AB58" s="3">
         <v>297000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>286000</v>
       </c>
       <c r="AC58" s="3">
         <v>286000</v>
       </c>
       <c r="AD58" s="3">
+        <v>286000</v>
+      </c>
+      <c r="AE58" s="3">
         <v>419000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>171000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>164000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>172600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>50700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>70500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>194000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>84600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>303200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>141800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>255100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>175900</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>525400</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E59" s="3">
         <v>689000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>682000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>719000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>706000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>653000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>607000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>526000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>565000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>587000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>570000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>584000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>805000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>839000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2030000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1360000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1293000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1330000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1456000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1452000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1482000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1385000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1409000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>35000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>31000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>62000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>95000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>92000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>90000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>114000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>97400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>47600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>48300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>92700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>80300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>75500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>68200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>57100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>70900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>161900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3333000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3165000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3282000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3403000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3352000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3230000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3646000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3718000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3712000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3869000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3767000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3573000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4235000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4148000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4236000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3816000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3651000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3859000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3798000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3637000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3862000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3921000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3810000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2199000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1970000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2124000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2329000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2525000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2313000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2299000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2398900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2099600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2236300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2436600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2425200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2381200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2106100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2151200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2094100</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2445100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4025000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4031000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4016000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4018000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4033000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3942000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3907000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4305000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3393000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3402000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3819000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3756000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4346000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4338000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4140000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4080000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4156000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4223000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4261000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4288000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4348000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3708000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3738000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2787000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2762000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1664000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1674000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1656000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1929000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1923000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1940700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2085600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2102500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2131500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2103700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2091900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2077900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2040300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2043600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2089900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>418000</v>
+      </c>
+      <c r="E62" s="3">
         <v>444000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>480000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>497000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>513000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>361000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>342000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>364000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>343000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>421000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>412000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>391000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>443000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>439000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1110000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1144000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1166000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1258000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1254000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1546000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1631000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1688000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1757000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>988000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>842000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>850000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>855000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1440000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1487000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1497000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1410900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1361000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1384400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1450900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1432800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1426800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1412600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1412500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1673100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>681600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8136000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8011000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8155000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8346000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8330000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7940000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8287000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8785000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7823000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8080000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8387000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8097000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9536000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9438000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9770000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9302000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9255000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9628000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9627000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9845000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10214000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9604000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9601000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6135000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5726000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4778000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4996000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5742000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5837000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5830000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5869800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5650000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5816900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6124100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6070800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5990500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5676500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5680300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5618700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5297400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7020000</v>
+      </c>
+      <c r="E72" s="3">
         <v>6777000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6570000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6867000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6745000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6545000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6412000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6840000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6620000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6325000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6152000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6010000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7796000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7632000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7454000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7239000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7005000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6830000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6671000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6582000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6527000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6321000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6296000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5979000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5903000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6036000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5942000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5757000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5598000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5461000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5336100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5127300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4958800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4722400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4531000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4712800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4557300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4374700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4215200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4538100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5621000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5479000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5442000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5989000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5923000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5720000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5532000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6156000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6093000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5841000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5828000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5768000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7551000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7441000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7224000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6775000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6889000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7050000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6948000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6646000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6649000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6367000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6428000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4757000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4611000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4724000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4706000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4457000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4394000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4274000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4225500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4066400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3960300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3910700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3716800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3825700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3612000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3403400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3218300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3709900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>277000</v>
+      </c>
+      <c r="E81" s="3">
         <v>242000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-262000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>158000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>224000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>157000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-405000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>234000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>303000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>206000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>154000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>50000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>204000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>217000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>255000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>273000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>416000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>129000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>96000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>247000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>65000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>358000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>111000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>129000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>220000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>194000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>172000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>160000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>230000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>203800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>271800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>225100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-146200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>184900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>212000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>189200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-293300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>83300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,67 +8990,68 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E83" s="3">
         <v>138000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>145000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>135000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>133000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>135000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>126000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>125000</v>
       </c>
       <c r="L83" s="3">
         <v>125000</v>
       </c>
       <c r="M83" s="3">
+        <v>125000</v>
+      </c>
+      <c r="N83" s="3">
         <v>123000</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q83" s="3">
         <v>157000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>178000</v>
       </c>
       <c r="R83" s="3">
         <v>178000</v>
       </c>
       <c r="S83" s="3">
+        <v>178000</v>
+      </c>
+      <c r="T83" s="3">
         <v>365000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>180000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>187000</v>
-      </c>
-      <c r="V83" s="3">
-        <v>195000</v>
       </c>
       <c r="W83" s="3">
         <v>195000</v>
@@ -8861,61 +9060,64 @@
         <v>195000</v>
       </c>
       <c r="Y83" s="3">
+        <v>195000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>229000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>115000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>224000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>112000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>115000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>110000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>107000</v>
       </c>
       <c r="AF83" s="3">
         <v>107000</v>
       </c>
       <c r="AG83" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AH83" s="3">
         <v>105500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>107500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>109100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>109200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>105800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>104900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>99800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>97300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>100200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>97800</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>586000</v>
+      </c>
+      <c r="E89" s="3">
         <v>152000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>619000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>368000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>579000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>82000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>679000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>347000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>454000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-128000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>868000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>176000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>280000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>891000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>347000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>332000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>116000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>542000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>142000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>280000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>342000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>376000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>481000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>327000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>263000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>184000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>357000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>427000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>40000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>570200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>251100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>270500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>34700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>556400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>224700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>338900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>60300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>442600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>230900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-143000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-162000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-111000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-119000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-161000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-155000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-165000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-190000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-208000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-185000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-239000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-195000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-96000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-154000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-177000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-172000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-152000</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-2000</v>
       </c>
       <c r="Z91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>153000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-171000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-135000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-102000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-127000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-117000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-152300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-125600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-108300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-160400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-170300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-135500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-123300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-130900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-145800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-120100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-95000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-130000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-122000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-88000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-94000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-143000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-147000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-138000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-175000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-55000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-103000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-239000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-282000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-732000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-298000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-388000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-254000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-157000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-139000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-914000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-185000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-617000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-102000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-147000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-120000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-109000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-103000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-173000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-104000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-121500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-126400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-105700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-160900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-181600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-315500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-122500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-132700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-61800</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-113500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,22 +10455,23 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="E96" s="3">
         <v>35000</v>
       </c>
       <c r="F96" s="3">
+        <v>35000</v>
+      </c>
+      <c r="G96" s="3">
         <v>36000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>24000</v>
       </c>
       <c r="H96" s="3">
         <v>24000</v>
@@ -10249,7 +10483,7 @@
         <v>24000</v>
       </c>
       <c r="K96" s="3">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="L96" s="3">
         <v>25000</v>
@@ -10258,49 +10492,49 @@
         <v>25000</v>
       </c>
       <c r="N96" s="3">
+        <v>25000</v>
+      </c>
+      <c r="O96" s="3">
         <v>26000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>40000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>39000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-40000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-39000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-82000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-41000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-40000</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-41000</v>
       </c>
       <c r="W96" s="3">
         <v>-41000</v>
       </c>
       <c r="X96" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-40000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-70000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-35000</v>
       </c>
       <c r="AC96" s="3">
         <v>-35000</v>
@@ -10315,37 +10549,40 @@
         <v>-35000</v>
       </c>
       <c r="AG96" s="3">
-        <v>-35200</v>
+        <v>-35000</v>
       </c>
       <c r="AH96" s="3">
         <v>-35200</v>
       </c>
       <c r="AI96" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-35500</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-35600</v>
       </c>
       <c r="AK96" s="3">
         <v>-35600</v>
       </c>
       <c r="AL96" s="3">
-        <v>-29400</v>
+        <v>-35600</v>
       </c>
       <c r="AM96" s="3">
         <v>-29400</v>
       </c>
       <c r="AN96" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-29700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-27600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-150000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-218000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-363000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-147000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-209000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-397000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-417000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>492000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-183000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-243000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>14000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-118000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-90000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-74000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-145000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-348000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-195000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-64000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-59000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>460000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-274000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-288000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>999000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-62000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-172000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-65000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-153000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-60000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-107700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-212200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-256300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>108100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-198500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-15800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-423700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-99200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E101" s="3">
         <v>22000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-25000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>20000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-11000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>15000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-25000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13000</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-53000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-50000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>13000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-13000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>44000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>27000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>13000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-17100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>12500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>9900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>10800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-32100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>338000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-203000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>131000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>334000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-387000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>94000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>712000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>251000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-497000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>585000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>101000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-102000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-388000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>97000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-149000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-454000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-340000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>334000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-58000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-187000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>105000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-471000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>118000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1171000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>69000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-84000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>206000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>193000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-222000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>377600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-47800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-135600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>131000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>27200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>28700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-85300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-75000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>23700</v>
       </c>
     </row>
